--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Strategic Metal and Energy Equity Fund of Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Strategic Metal and Energy Equity Fund of Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="28">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Strategic Metal and Energy Equity Fund of Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -89,7 +89,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -99,9 +99,6 @@
   </si>
   <si>
     <t>Benchmark Riskometer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Benchmark name - NYSE Arca Gold Miners Index and the S&amp;P Oil &amp; Gas Exploration &amp; Production Select Industry Index </t>
   </si>
 </sst>
 </file>
@@ -819,7 +816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J47"/>
+  <dimension ref="B1:J46"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="23" width="10.0" collapsed="true"/>
@@ -913,10 +910,10 @@
         <v>12</v>
       </c>
       <c r="F5" s="9">
-        <v>9234.02</v>
+        <v>9031.19</v>
       </c>
       <c r="G5" s="10">
-        <v>0.9963098770343</v>
+        <v>0.9951180481331</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>12</v>
@@ -941,13 +938,13 @@
         <v>16</v>
       </c>
       <c r="E7" s="14">
-        <v>116070.893</v>
+        <v>104607.1855</v>
       </c>
       <c r="F7" s="15">
-        <v>9234.02</v>
+        <v>9031.19</v>
       </c>
       <c r="G7" s="16">
-        <v>0.9963098770343</v>
+        <v>0.9951180481331</v>
       </c>
       <c r="H7" s="15" t="s">
         <v>12</v>
@@ -978,10 +975,10 @@
         <v>12</v>
       </c>
       <c r="F9" s="9">
-        <v>67.81</v>
+        <v>54.12</v>
       </c>
       <c r="G9" s="10">
-        <v>0.0073163987907</v>
+        <v>0.0059633103461</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>12</v>
@@ -1012,10 +1009,10 @@
         <v>12</v>
       </c>
       <c r="F11" s="18">
-        <v>-33.609125299999505</v>
+        <v>-9.813864700001432</v>
       </c>
       <c r="G11" s="19">
-        <v>-0.003626275825141833</v>
+        <v>-0.0010813584793264886</v>
       </c>
       <c r="H11" s="18" t="s">
         <v>12</v>
@@ -1038,10 +1035,10 @@
         <v>12</v>
       </c>
       <c r="F12" s="18">
-        <v>9268.2208747</v>
+        <v>9075.4961353</v>
       </c>
       <c r="G12" s="19">
-        <v>0.9999999999998581</v>
+        <v>0.9999999999998735</v>
       </c>
       <c r="H12" s="18" t="s">
         <v>12</v>
@@ -1139,11 +1136,6 @@
     <row r="46" ht="15">
       <c r="B46" s="23" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="47" ht="15">
-      <c r="B47" s="23" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
